--- a/master/result/59_穿越商海_江南女商之路/59_穿越商海_江南女商之路.xlsx
+++ b/master/result/59_穿越商海_江南女商之路/59_穿越商海_江南女商之路.xlsx
@@ -397,566 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>flat</v>
       </c>
       <c r="B2" t="str">
-        <v>flat</v>
+        <v>/flat/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>平坦的</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>panorama</v>
       </c>
       <c r="B3" t="str">
-        <v>panorama</v>
+        <v>/panorama/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>全景</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>study</v>
       </c>
       <c r="B4" t="str">
-        <v>study</v>
+        <v>/ˈstʌdi/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>学习</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>son</v>
       </c>
       <c r="B5" t="str">
-        <v>son</v>
+        <v>/son/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>儿子</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>intention</v>
       </c>
       <c r="B6" t="str">
-        <v>intention</v>
+        <v>/intention/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>意图</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>embark</v>
       </c>
       <c r="B7" t="str">
-        <v>embark</v>
+        <v>/embark/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>着手</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>barely</v>
       </c>
       <c r="B8" t="str">
-        <v>barely</v>
+        <v>/ˈbeəli/</v>
       </c>
       <c r="C8" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>仅仅</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>leadership</v>
       </c>
       <c r="B9" t="str">
-        <v>leadership</v>
+        <v>/leadership/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>领导</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>target</v>
       </c>
       <c r="B10" t="str">
-        <v>target</v>
+        <v>/ˈtɑːɡɪt/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>目标</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>wrong</v>
       </c>
       <c r="B11" t="str">
-        <v>wrong</v>
+        <v>/wrong/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>错误的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>questionnaire</v>
       </c>
       <c r="B12" t="str">
-        <v>questionnaire</v>
+        <v>/questionnaire/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>问卷</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>debate</v>
       </c>
       <c r="B13" t="str">
-        <v>debate</v>
+        <v>/dɪˈbeɪt/</v>
       </c>
       <c r="C13" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>辩论</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cite</v>
       </c>
       <c r="B14" t="str">
-        <v>cite</v>
+        <v>/cite/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>引用</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>cabbage</v>
       </c>
       <c r="B15" t="str">
-        <v>cabbage</v>
+        <v>/cabbage/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>卷心菜</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>cherish</v>
       </c>
       <c r="B16" t="str">
-        <v>cherish</v>
+        <v>/cherish/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>珍爱</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>hostile</v>
       </c>
       <c r="B17" t="str">
-        <v>hostile</v>
+        <v>/hostile/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>敌对的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>yield</v>
       </c>
       <c r="B18" t="str">
-        <v>yield</v>
+        <v>/yield/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>屈服</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>metropolitan</v>
       </c>
       <c r="B19" t="str">
-        <v>metropolitan</v>
+        <v>/metropolitan/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>大都市</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>beyond</v>
       </c>
       <c r="B20" t="str">
-        <v>beyond</v>
+        <v>/beyond/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>超出</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>tremble</v>
       </c>
       <c r="B21" t="str">
-        <v>tremble</v>
+        <v>/ˈtrembl/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>颤抖</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>cocaine</v>
       </c>
       <c r="B22" t="str">
-        <v>cocaine</v>
+        <v>/cocaine/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>可卡因</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>disgust</v>
       </c>
       <c r="B23" t="str">
-        <v>disgust</v>
+        <v>/disgust/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>厌恶</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>solemn</v>
       </c>
       <c r="B24" t="str">
-        <v>solemn</v>
+        <v>/solemn/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>庄严的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>unify</v>
       </c>
       <c r="B25" t="str">
-        <v>unify</v>
+        <v>/unify/</v>
       </c>
       <c r="C25" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>统一</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>allowance</v>
       </c>
       <c r="B26" t="str">
-        <v>allowance</v>
+        <v>/allowance/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>津贴</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>hungry</v>
       </c>
       <c r="B27" t="str">
-        <v>hungry</v>
+        <v>/hungry/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>饥饿的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>drag</v>
       </c>
       <c r="B28" t="str">
-        <v>drag</v>
+        <v>/dræɡ/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>拖</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>paradox</v>
       </c>
       <c r="B29" t="str">
-        <v>paradox</v>
+        <v>/paradox/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>悖论</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>crazy</v>
       </c>
       <c r="B30" t="str">
-        <v>crazy</v>
+        <v>/crazy/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>疯狂地</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>clean</v>
       </c>
       <c r="B31" t="str">
-        <v>clean</v>
+        <v>/kliːn/</v>
       </c>
       <c r="C31" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D31" t="str">
         <v>清洁的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>token</v>
       </c>
       <c r="B32" t="str">
-        <v>token</v>
+        <v>/token/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>标志</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>exchange</v>
       </c>
       <c r="B33" t="str">
-        <v>exchange</v>
+        <v>/ɪksˈtʃeɪndʒ/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>交换</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>striking</v>
       </c>
       <c r="B34" t="str">
-        <v>striking</v>
+        <v>/striking/</v>
       </c>
       <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>显著的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>any</v>
       </c>
       <c r="B35" t="str">
-        <v>any</v>
+        <v>/any/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>任何</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>pyramid</v>
       </c>
       <c r="B36" t="str">
-        <v>pyramid</v>
+        <v>/pyramid/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>金字塔</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>tropic</v>
       </c>
       <c r="B37" t="str">
-        <v>tropic</v>
+        <v>/tropic/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>热带</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>heal</v>
       </c>
       <c r="B38" t="str">
-        <v>heal</v>
+        <v>/heal/</v>
       </c>
       <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>治愈</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>most</v>
       </c>
       <c r="B39" t="str">
-        <v>most</v>
+        <v>/most/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>大多数</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>step</v>
       </c>
       <c r="B40" t="str">
-        <v>step</v>
+        <v>/step/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>步骤</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>chase</v>
       </c>
       <c r="B41" t="str">
-        <v>chase</v>
+        <v>/chase/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>追逐</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>verbal</v>
       </c>
       <c r="B42" t="str">
-        <v>verbal</v>
+        <v>/verbal/</v>
       </c>
       <c r="C42" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D42" t="str">
         <v>口头的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>smooth</v>
       </c>
       <c r="B43" t="str">
-        <v>smooth</v>
+        <v>/smooth/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>平滑地</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>ideology</v>
       </c>
       <c r="B44" t="str">
-        <v>ideology</v>
+        <v>/ideology/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>意识形态</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>front</v>
       </c>
       <c r="B45" t="str">
-        <v>front</v>
+        <v>/front/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>前面</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>planet</v>
       </c>
       <c r="B46" t="str">
-        <v>planet</v>
+        <v>/planet/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>行星</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>amuse</v>
       </c>
       <c r="B47" t="str">
-        <v>amuse</v>
+        <v>/amuse/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>娱乐</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>exempt</v>
       </c>
       <c r="B48" t="str">
-        <v>exempt</v>
+        <v>/exempt/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>免除</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>inclusive</v>
       </c>
       <c r="B49" t="str">
-        <v>inclusive</v>
+        <v>/inclusive/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>包括的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>distance</v>
       </c>
       <c r="B50" t="str">
-        <v>distance</v>
+        <v>/distance/</v>
       </c>
       <c r="C50" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>距离</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>